--- a/QA_Manual_SauceDemo.xlsx
+++ b/QA_Manual_SauceDemo.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="Rfa3f02810dfc4512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos de prueba" sheetId="2" r:id="R4118009e6b6e495b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejecución" sheetId="3" r:id="Ra780bb2a6df24f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte de defectos" sheetId="4" r:id="Rfada932610614f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" r:id="Rbeef6bf95ac24730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos de prueba" sheetId="2" r:id="Rccf6da22f8cb496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejecución" sheetId="3" r:id="R98e5f5c2d482472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte de defectos" sheetId="4" r:id="Re657601add684a6d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,7 +319,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -330,7 +330,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -716,8 +716,8 @@
         <x:v>Defectos registrados</x:v>
       </x:c>
       <x:c r="E10" s="22" t="n">
-        <x:f>COUNTIF('Reporte de defectos'!A7:A100,"BUG-*")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTA('Reporte de defectos'!A7:A100)</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str"/>
       <x:c r="G10" s="2"/>
@@ -756,7 +756,7 @@
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
       <x:c r="A13" s="26" t="str">
-        <x:v>Los flujos críticos incluidos en el alcance funcionaron conforme a lo esperado. No se identificaron defectos durante esta primera ronda.</x:v>
+        <x:v>Ronda funcional inicial: 3 casos aprobados. Pruebas exploratorias con usuarios de demostración: 5 defectos documentados.</x:v>
       </x:c>
       <x:c r="B13" s="27"/>
       <x:c r="C13" s="27"/>
@@ -4807,66 +4807,160 @@
       <x:c r="K6" s="2"/>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
-      <x:c r="A7" s="35"/>
-      <x:c r="B7" s="35"/>
-      <x:c r="C7" s="35"/>
-      <x:c r="D7" s="35"/>
-      <x:c r="E7" s="35"/>
-      <x:c r="F7" s="35"/>
-      <x:c r="G7" s="35"/>
-      <x:c r="H7" s="35"/>
+      <x:c r="A7" s="35" t="str">
+        <x:v>BUG-001</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>El carrito se mantiene al cambiar de usuario</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>Carrito / Autenticación</x:v>
+      </x:c>
+      <x:c r="D7" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="E7" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="F7" s="35" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="G7" s="35" t="str">
+        <x:v>1. Agregar Sauce Labs Backpack con standard_user.
+2. Iniciar sesión con problem_user.
+3. Abrir el carrito.</x:v>
+      </x:c>
+      <x:c r="H7" s="35" t="str">
+        <x:v>Esperado: carrito vacío para el nuevo usuario.
+Actual: Backpack permanece con cantidad 1.</x:v>
+      </x:c>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="2"/>
       <x:c r="K7" s="2"/>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
-      <x:c r="A8" s="35"/>
-      <x:c r="B8" s="35"/>
-      <x:c r="C8" s="35"/>
-      <x:c r="D8" s="35"/>
-      <x:c r="E8" s="35"/>
-      <x:c r="F8" s="35"/>
-      <x:c r="G8" s="35"/>
-      <x:c r="H8" s="35"/>
+      <x:c r="A8" s="35" t="str">
+        <x:v>BUG-002</x:v>
+      </x:c>
+      <x:c r="B8" s="35" t="str">
+        <x:v>Todas las imágenes del catálogo son una imagen de error</x:v>
+      </x:c>
+      <x:c r="C8" s="35" t="str">
+        <x:v>Catálogo</x:v>
+      </x:c>
+      <x:c r="D8" s="35" t="str">
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="E8" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="F8" s="35" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="G8" s="35" t="str">
+        <x:v>1. Iniciar sesión con problem_user.
+2. Abrir catálogo.
+3. Comparar las imágenes.</x:v>
+      </x:c>
+      <x:c r="H8" s="35" t="str">
+        <x:v>Esperado: imagen propia por producto.
+Actual: seis imágenes apuntan a /assets/sl-404-Cq1a9k9X.jpg.</x:v>
+      </x:c>
       <x:c r="I8" s="2"/>
       <x:c r="J8" s="2"/>
       <x:c r="K8" s="2"/>
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
-      <x:c r="A9" s="35"/>
-      <x:c r="B9" s="35"/>
-      <x:c r="C9" s="35"/>
-      <x:c r="D9" s="35"/>
-      <x:c r="E9" s="35"/>
-      <x:c r="F9" s="35"/>
-      <x:c r="G9" s="35"/>
-      <x:c r="H9" s="35"/>
+      <x:c r="A9" s="35" t="str">
+        <x:v>BUG-003</x:v>
+      </x:c>
+      <x:c r="B9" s="35" t="str">
+        <x:v>El apellido se registra en el campo de nombre</x:v>
+      </x:c>
+      <x:c r="C9" s="35" t="str">
+        <x:v>Checkout</x:v>
+      </x:c>
+      <x:c r="D9" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="E9" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="F9" s="35" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="G9" s="35" t="str">
+        <x:v>1. Abrir checkout con problem_user.
+2. Ingresar Ana en nombre.
+3. Ingresar Pérez en apellido.
+4. Continuar.</x:v>
+      </x:c>
+      <x:c r="H9" s="35" t="str">
+        <x:v>Esperado: cada campo conserva su valor.
+Actual: Pérez sobrescribe el nombre y aparece Error: Last Name is required.</x:v>
+      </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
       <x:c r="K9" s="2"/>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
-      <x:c r="A10" s="35"/>
-      <x:c r="B10" s="35"/>
-      <x:c r="C10" s="35"/>
-      <x:c r="D10" s="35"/>
-      <x:c r="E10" s="35"/>
-      <x:c r="F10" s="35"/>
-      <x:c r="G10" s="35"/>
-      <x:c r="H10" s="35"/>
+      <x:c r="A10" s="35" t="str">
+        <x:v>BUG-004</x:v>
+      </x:c>
+      <x:c r="B10" s="35" t="str">
+        <x:v>Sauce Labs Fleece Jacket no se agrega al carrito</x:v>
+      </x:c>
+      <x:c r="C10" s="35" t="str">
+        <x:v>Catálogo / Carrito</x:v>
+      </x:c>
+      <x:c r="D10" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="E10" s="35" t="str">
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="F10" s="35" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="G10" s="35" t="str">
+        <x:v>1. Iniciar sesión con error_user.
+2. Seleccionar Add to cart en Fleece Jacket.</x:v>
+      </x:c>
+      <x:c r="H10" s="35" t="str">
+        <x:v>Esperado: botón cambia a Remove y contador aumenta.
+Actual: no hay cambio de estado.</x:v>
+      </x:c>
       <x:c r="I10" s="2"/>
       <x:c r="J10" s="2"/>
       <x:c r="K10" s="2"/>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
-      <x:c r="A11" s="35"/>
-      <x:c r="B11" s="35"/>
-      <x:c r="C11" s="35"/>
-      <x:c r="D11" s="35"/>
-      <x:c r="E11" s="35"/>
-      <x:c r="F11" s="35"/>
-      <x:c r="G11" s="35"/>
-      <x:c r="H11" s="35"/>
+      <x:c r="A11" s="35" t="str">
+        <x:v>BUG-005</x:v>
+      </x:c>
+      <x:c r="B11" s="35" t="str">
+        <x:v>Ordenar por precio muestra una alerta de JavaScript</x:v>
+      </x:c>
+      <x:c r="C11" s="35" t="str">
+        <x:v>Catálogo / Ordenamiento</x:v>
+      </x:c>
+      <x:c r="D11" s="35" t="str">
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="str">
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="F11" s="35" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="G11" s="35" t="str">
+        <x:v>1. Iniciar sesión con error_user.
+2. Elegir Price (low to high).</x:v>
+      </x:c>
+      <x:c r="H11" s="35" t="str">
+        <x:v>Esperado: productos ordenados por precio.
+Actual: alerta Sorting is broken! This error has been reported to Backtrace.</x:v>
+      </x:c>
       <x:c r="I11" s="2"/>
       <x:c r="J11" s="2"/>
       <x:c r="K11" s="2"/>
